--- a/CodeSystem-resultcode-cs.xlsx
+++ b/CodeSystem-resultcode-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:41:16+00:00</t>
+    <t>2026-06-24T16:59:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-resultcode-cs.xlsx
+++ b/CodeSystem-resultcode-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:59:36+00:00</t>
+    <t>2026-06-24T18:15:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-resultcode-cs.xlsx
+++ b/CodeSystem-resultcode-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T18:15:06+00:00</t>
+    <t>2026-06-24T18:25:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-resultcode-cs.xlsx
+++ b/CodeSystem-resultcode-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T18:25:37+00:00</t>
+    <t>2026-06-24T18:50:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-resultcode-cs.xlsx
+++ b/CodeSystem-resultcode-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.1</t>
+    <t>0.3.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T18:50:27+00:00</t>
+    <t>2026-06-25T06:56:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-resultcode-cs.xlsx
+++ b/CodeSystem-resultcode-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.2</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T06:56:03+00:00</t>
+    <t>2026-06-25T07:52:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
